--- a/CheckWeigherFood/bin/Debug/Template/FormatExcel.xlsx
+++ b/CheckWeigherFood/bin/Debug/Template/FormatExcel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Unilever\UCC\Oral\UCC.ORAL.SPC.CHECK_WEIGHT\CheckWeigherFood\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC0DA3A-FD42-49E3-8ED3-7F491CC5EA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9620BA93-E577-45B2-93F3-D8CFD22C6342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{70070A5B-A491-4AF3-BC84-71C5139C360B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{70070A5B-A491-4AF3-BC84-71C5139C360B}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>BÁO CÁO DỮ LIỆU CÂN PACKING ORAL</t>
   </si>
@@ -88,15 +88,6 @@
   </si>
   <si>
     <t>Max (g)</t>
-  </si>
-  <si>
-    <t>Số dữ liệu Over</t>
-  </si>
-  <si>
-    <t>Số dữ liệu Accept</t>
-  </si>
-  <si>
-    <t>Số dữ liệu Reject</t>
   </si>
 </sst>
 </file>
@@ -293,50 +284,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC243F90-9D67-4E75-A645-6B53CDC24AEF}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -664,65 +655,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="20"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="9"/>
+      <c r="D3" s="14"/>
       <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
     </row>
-    <row r="4" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="10"/>
+      <c r="D4" s="15"/>
       <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
     </row>
-    <row r="5" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -731,132 +722,100 @@
       <c r="H6" s="3"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="7"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="5"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="5"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="7"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="5"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="7"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="5"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:9" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="7"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="5"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="H12" s="3"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I11"/>
+  <mergeCells count="19">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -865,21 +824,26 @@
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="D3:D5"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F11:I11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="9111f2b4-c723-4ea7-a79a-067c9b02325f">
@@ -897,15 +861,6 @@
     <_activity xmlns="bded958f-0855-4047-9b5e-1e0844a68dea" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1142,6 +1097,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D13D16C2-9F9D-4634-B365-776AC335773A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05A034E0-EB47-4925-82DA-655EB835327F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="bded958f-0855-4047-9b5e-1e0844a68dea"/>
@@ -1154,14 +1117,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="9111f2b4-c723-4ea7-a79a-067c9b02325f"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D13D16C2-9F9D-4634-B365-776AC335773A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
